--- a/project_1/filename.xlsx
+++ b/project_1/filename.xlsx
@@ -579,43 +579,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>101766</v>
       </c>
       <c r="C3" t="n">
-        <v>940</v>
+        <v>71518</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -625,43 +625,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4250949.834</v>
+        <v>165201645.6229782</v>
       </c>
       <c r="C4" t="n">
-        <v>28138010.238</v>
+        <v>54330400.69494724</v>
       </c>
       <c r="D4" t="n">
-        <v>4.331</v>
+        <v>2.024006053102215</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>3.715641766405283</v>
       </c>
       <c r="F4" t="n">
-        <v>4.933</v>
+        <v>5.754436648782501</v>
       </c>
       <c r="G4" t="n">
-        <v>4.631</v>
+        <v>4.395986871843248</v>
       </c>
       <c r="H4" t="n">
-        <v>49.249</v>
+        <v>43.09564098028811</v>
       </c>
       <c r="I4" t="n">
-        <v>1.658316633266533</v>
+        <v>1.339657697865773</v>
       </c>
       <c r="J4" t="n">
-        <v>14.59277833500501</v>
+        <v>16.02127659574468</v>
       </c>
       <c r="K4" t="n">
-        <v>0.052</v>
+        <v>0.3693571526836075</v>
       </c>
       <c r="L4" t="n">
-        <v>0.016</v>
+        <v>0.1978362124874713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.211</v>
+        <v>0.635565906098304</v>
       </c>
       <c r="N4" t="n">
-        <v>6.705</v>
+        <v>7.422606764538254</v>
       </c>
     </row>
     <row r="5">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4254525</v>
+        <v>152388987</v>
       </c>
       <c r="C5" t="n">
-        <v>5189278.5</v>
+        <v>45505143</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>7</v>
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -717,43 +717,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1958644.408111783</v>
+        <v>102640295.9834572</v>
       </c>
       <c r="C6" t="n">
-        <v>37288859.95540194</v>
+        <v>38696359.3465342</v>
       </c>
       <c r="D6" t="n">
-        <v>2.157798668804645</v>
+        <v>1.445402829756121</v>
       </c>
       <c r="E6" t="n">
-        <v>11.39745155295261</v>
+        <v>5.280165509299271</v>
       </c>
       <c r="F6" t="n">
-        <v>3.695696033113271</v>
+        <v>4.064080834283899</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1544872467312</v>
+        <v>2.985107767471267</v>
       </c>
       <c r="H6" t="n">
-        <v>16.78113838825023</v>
+        <v>19.67436224914212</v>
       </c>
       <c r="I6" t="n">
-        <v>1.815592216670801</v>
+        <v>1.70568913463414</v>
       </c>
       <c r="J6" t="n">
-        <v>7.598527388772363</v>
+        <v>8.12690665572639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5211214518397487</v>
+        <v>1.267265096532678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.133273259740136</v>
+        <v>0.9304722684224636</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6138858654960675</v>
+        <v>1.262863290097324</v>
       </c>
       <c r="N6" t="n">
-        <v>2.169027357983223</v>
+        <v>1.933600144997429</v>
       </c>
     </row>
     <row r="7">
@@ -766,7 +766,7 @@
         <v>12522</v>
       </c>
       <c r="C7" t="n">
-        <v>12447</v>
+        <v>135</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -809,43 +809,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7555146</v>
+        <v>443867222</v>
       </c>
       <c r="C8" t="n">
-        <v>115196778</v>
+        <v>189502619</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
         <v>25</v>
-      </c>
-      <c r="F8" t="n">
-        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -876,19 +876,19 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>367</v>
+        <v>46631</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>980</v>
+        <v>85027</v>
       </c>
       <c r="L9" t="n">
-        <v>985</v>
+        <v>90383</v>
       </c>
       <c r="M9" t="n">
-        <v>847</v>
+        <v>67630</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
